--- a/data/trans_orig/IQ21C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Clase-trans_orig.xlsx
@@ -15530,7 +15530,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -19892,7 +19892,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -19953,7 +19953,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -19988,7 +19988,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20286,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -20392,12 +20392,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -20407,12 +20407,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -20427,12 +20427,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -20442,12 +20442,12 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20508,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -21063,7 +21063,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -27467,7 +27467,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -27482,7 +27482,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -27689,7 +27689,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -27815,7 +27815,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -28461,12 +28461,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -30345,7 +30345,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -30365,7 +30365,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -30380,7 +30380,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -30406,7 +30406,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -30421,7 +30421,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -30476,7 +30476,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -30491,7 +30491,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -30517,7 +30517,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -30587,7 +30587,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -30663,7 +30663,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -30678,7 +30678,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -30698,7 +30698,7 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -30713,7 +30713,7 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -30739,7 +30739,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -30754,7 +30754,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -30809,7 +30809,7 @@
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -30824,7 +30824,7 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -31072,7 +31072,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -31107,7 +31107,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -31142,7 +31142,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -31157,7 +31157,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -31198,7 +31198,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -31253,7 +31253,7 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -31268,7 +31268,7 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -31329,7 +31329,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -31344,7 +31344,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -31359,12 +31359,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -31374,12 +31374,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -31455,7 +31455,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -31475,7 +31475,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -31490,7 +31490,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -41741,7 +41741,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -41756,7 +41756,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
